--- a/files/energy/input/load_emulator/input_emulator_v2/1. usage_probability_v2.xlsx
+++ b/files/energy/input/load_emulator/input_emulator_v2/1. usage_probability_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rsericerca-my.sharepoint.com/personal/rollo_rse-web_it/Documents/Desktop/CACER simulator - public repo/CACER-simulator/files/energy/input/load_emulator/input_emulator_v2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="335" documentId="11_59AB53411A6BFA624CF54379889ED3FCF7CC7820" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37848E3B-AF9C-44AC-BB54-62A5BFE1A744}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="11_59AB53411A6BFA624CF54379889ED3FCF7CC7820" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0789455C-878B-4E2D-B68D-27B270BE89A1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="working_day" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     Information no available: equal to washing_machine</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{345E653F-3282-4BB6-B2F9-944813E8D8A9}">
+    <comment ref="K1" authorId="3" shapeId="0" xr:uid="{345E653F-3282-4BB6-B2F9-944813E8D8A9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -221,7 +221,7 @@
     Information no available: equal to washing_machine</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{12F2D9EA-8290-4EBD-95A0-22F667F8157D}">
+    <comment ref="K1" authorId="3" shapeId="0" xr:uid="{12F2D9EA-8290-4EBD-95A0-22F667F8157D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -666,9 +666,6 @@
     <t>dehumidifier</t>
   </si>
   <si>
-    <t>electric_hob</t>
-  </si>
-  <si>
     <t>iron</t>
   </si>
   <si>
@@ -697,6 +694,9 @@
   </si>
   <si>
     <t>screen</t>
+  </si>
+  <si>
+    <t>induction_hob</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1125,7 @@
   <threadedComment ref="H1" dT="2026-03-24T15:03:57.74" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{BC644381-17E1-42D6-9A9A-359FC117774B}">
     <text>Information no available: equal to washing_machine</text>
   </threadedComment>
-  <threadedComment ref="I1" dT="2026-03-24T15:04:07.09" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{345E653F-3282-4BB6-B2F9-944813E8D8A9}">
+  <threadedComment ref="K1" dT="2026-03-24T15:04:07.09" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{345E653F-3282-4BB6-B2F9-944813E8D8A9}">
     <text>Zenodo db</text>
   </threadedComment>
   <threadedComment ref="L1" dT="2026-03-24T15:04:22.76" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{59AA8EEC-CCA3-46FB-A8BB-8FE1007B11EB}">
@@ -1175,7 +1175,7 @@
   <threadedComment ref="H1" dT="2026-03-24T15:03:57.74" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{07C19E1C-D168-4C85-A1C7-60F56A2E99CC}">
     <text>Information no available: equal to washing_machine</text>
   </threadedComment>
-  <threadedComment ref="I1" dT="2026-03-24T15:04:07.09" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{12F2D9EA-8290-4EBD-95A0-22F667F8157D}">
+  <threadedComment ref="K1" dT="2026-03-24T15:04:07.09" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{12F2D9EA-8290-4EBD-95A0-22F667F8157D}">
     <text>Zenodo db</text>
   </threadedComment>
   <threadedComment ref="L1" dT="2026-03-24T15:04:22.76" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{C5E655D0-4EC1-4C75-AA79-9BF684AF2CD7}">
@@ -1255,31 +1255,31 @@
         <v>3</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>8</v>
@@ -1288,16 +1288,16 @@
         <v>9</v>
       </c>
       <c r="T1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="V1" s="7" t="s">
         <v>111</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X1" s="7" t="s">
         <v>10</v>
@@ -1306,13 +1306,13 @@
         <v>109</v>
       </c>
       <c r="Z1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="AC1" s="7" t="s">
         <v>11</v>
@@ -1441,10 +1441,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="3">
-        <v>0</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="J3" s="3">
-        <v>5.5555555555555552E-2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -1633,10 +1633,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>0</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="J5" s="3">
-        <v>5.5555555555555552E-2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -2785,13 +2785,13 @@
         <v>0</v>
       </c>
       <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>4.9261083743842361E-4</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0</v>
       </c>
       <c r="L17" s="3">
         <f t="shared" si="1"/>
@@ -3073,13 +3073,13 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>4.9261083743842361E-4</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
       </c>
       <c r="L20" s="3">
         <f t="shared" si="1"/>
@@ -3169,13 +3169,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>4.9261083743842361E-4</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
       </c>
       <c r="L21" s="3">
         <f t="shared" si="1"/>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>1.477832512315271E-3</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
       </c>
       <c r="L23" s="3">
         <f t="shared" si="1"/>
@@ -3457,13 +3457,13 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>2.4630541871921178E-3</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="1"/>
@@ -3553,13 +3553,13 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
         <v>2.4630541871921178E-3</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" si="1"/>
@@ -3649,13 +3649,13 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>4.4334975369458131E-3</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="1"/>
@@ -3745,13 +3745,13 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>5.9113300492610842E-3</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="1"/>
@@ -3841,13 +3841,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
         <v>9.3596059113300496E-3</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="1"/>
@@ -3937,13 +3937,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>8.8669950738916262E-3</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="1"/>
@@ -4033,13 +4033,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
         <v>1.083743842364532E-2</v>
-      </c>
-      <c r="J30" s="3">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3">
-        <v>0</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" si="1"/>
@@ -4129,13 +4129,13 @@
         <v>0</v>
       </c>
       <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
         <v>1.8719211822660099E-2</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3">
-        <v>0</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" si="1"/>
@@ -4225,13 +4225,13 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>2.463054187192118E-2</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" si="1"/>
@@ -4321,13 +4321,13 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>1.8719211822660099E-2</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
       </c>
       <c r="L33" s="3">
         <f t="shared" si="1"/>
@@ -4417,13 +4417,13 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
         <v>2.266009852216749E-2</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0</v>
       </c>
       <c r="L34" s="3">
         <f t="shared" ref="L34:L65" si="7">1/96</f>
@@ -4513,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K35" s="3">
         <v>1.6256157635467981E-2</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L35" s="3">
         <f t="shared" si="7"/>
@@ -4609,13 +4609,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I36" s="3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
         <v>1.428571428571429E-2</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0</v>
       </c>
       <c r="L36" s="3">
         <f t="shared" si="7"/>
@@ -4705,13 +4705,13 @@
         <v>0</v>
       </c>
       <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3">
         <v>8.3743842364532011E-3</v>
-      </c>
-      <c r="J37" s="3">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3">
-        <v>0</v>
       </c>
       <c r="L37" s="3">
         <f t="shared" si="7"/>
@@ -4801,13 +4801,13 @@
         <v>0</v>
       </c>
       <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3">
         <v>8.8669950738916262E-3</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0</v>
-      </c>
-      <c r="K38" s="3">
-        <v>0</v>
       </c>
       <c r="L38" s="3">
         <f t="shared" si="7"/>
@@ -4897,13 +4897,13 @@
         <v>0</v>
       </c>
       <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K39" s="3">
         <v>7.3891625615763543E-3</v>
-      </c>
-      <c r="J39" s="3">
-        <v>0</v>
-      </c>
-      <c r="K39" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L39" s="3">
         <f t="shared" si="7"/>
@@ -4993,13 +4993,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3">
         <v>1.03448275862069E-2</v>
-      </c>
-      <c r="J40" s="3">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3">
-        <v>0</v>
       </c>
       <c r="L40" s="3">
         <f t="shared" si="7"/>
@@ -5089,13 +5089,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I41" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>4.9261083743842374E-3</v>
-      </c>
-      <c r="J41" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
       </c>
       <c r="L41" s="3">
         <f t="shared" si="7"/>
@@ -5185,13 +5185,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I42" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K42" s="3">
         <v>8.8669950738916262E-3</v>
-      </c>
-      <c r="J42" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K42" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L42" s="3">
         <f t="shared" si="7"/>
@@ -5281,13 +5281,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2.3809523809523812E-2</v>
+      </c>
+      <c r="K43" s="3">
         <v>8.8669950738916262E-3</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
-        <v>2.3809523809523812E-2</v>
       </c>
       <c r="L43" s="3">
         <f t="shared" si="7"/>
@@ -5377,13 +5377,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I44" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J44" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K44" s="3">
         <v>1.182266009852217E-2</v>
-      </c>
-      <c r="J44" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K44" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L44" s="3">
         <f t="shared" si="7"/>
@@ -5473,13 +5473,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K45" s="3">
         <v>6.4039408866995084E-3</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L45" s="3">
         <f t="shared" si="7"/>
@@ -5569,13 +5569,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I46" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K46" s="3">
         <v>1.133004926108374E-2</v>
-      </c>
-      <c r="J46" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K46" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L46" s="3">
         <f t="shared" si="7"/>
@@ -5665,13 +5665,13 @@
         <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>1.03448275862069E-2</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
       </c>
       <c r="L47" s="3">
         <f t="shared" si="7"/>
@@ -5761,13 +5761,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K48" s="3">
         <v>1.5763546798029559E-2</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L48" s="3">
         <f t="shared" si="7"/>
@@ -5857,13 +5857,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>1.428571428571429E-2</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
       </c>
       <c r="L49" s="3">
         <f t="shared" si="7"/>
@@ -5953,13 +5953,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K50" s="3">
         <v>1.7733990147783249E-2</v>
-      </c>
-      <c r="J50" s="3">
-        <v>0</v>
-      </c>
-      <c r="K50" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L50" s="3">
         <f t="shared" si="7"/>
@@ -6049,13 +6049,13 @@
         <v>0</v>
       </c>
       <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K51" s="3">
         <v>1.527093596059113E-2</v>
-      </c>
-      <c r="J51" s="3">
-        <v>0</v>
-      </c>
-      <c r="K51" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L51" s="3">
         <f t="shared" si="7"/>
@@ -6145,13 +6145,13 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>1.970443349753695E-2</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
       </c>
       <c r="L52" s="3">
         <f t="shared" si="7"/>
@@ -6241,13 +6241,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3">
         <v>1.330049261083744E-2</v>
-      </c>
-      <c r="J53" s="3">
-        <v>0</v>
-      </c>
-      <c r="K53" s="3">
-        <v>0</v>
       </c>
       <c r="L53" s="3">
         <f t="shared" si="7"/>
@@ -6337,13 +6337,13 @@
         <v>0</v>
       </c>
       <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3">
         <v>1.8226600985221671E-2</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
-      </c>
-      <c r="K54" s="3">
-        <v>0</v>
       </c>
       <c r="L54" s="3">
         <f t="shared" si="7"/>
@@ -6433,13 +6433,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K55" s="3">
         <v>1.527093596059113E-2</v>
-      </c>
-      <c r="J55" s="3">
-        <v>0</v>
-      </c>
-      <c r="K55" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L55" s="3">
         <f t="shared" si="7"/>
@@ -6529,13 +6529,13 @@
         <v>0</v>
       </c>
       <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K56" s="3">
         <v>2.0689655172413789E-2</v>
-      </c>
-      <c r="J56" s="3">
-        <v>0</v>
-      </c>
-      <c r="K56" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L56" s="3">
         <f t="shared" si="7"/>
@@ -6625,13 +6625,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>1.8226600985221671E-2</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
-        <v>0</v>
       </c>
       <c r="L57" s="3">
         <f t="shared" si="7"/>
@@ -6721,13 +6721,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>1.379310344827586E-2</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
       </c>
       <c r="L58" s="3">
         <f t="shared" si="7"/>
@@ -6817,13 +6817,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>1.8719211822660099E-2</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
       </c>
       <c r="L59" s="3">
         <f t="shared" si="7"/>
@@ -6913,13 +6913,13 @@
         <v>0</v>
       </c>
       <c r="I60" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J60" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K60" s="3">
         <v>1.6748768472906399E-2</v>
-      </c>
-      <c r="J60" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K60" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L60" s="3">
         <f t="shared" si="7"/>
@@ -7009,13 +7009,13 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K61" s="3">
         <v>1.231527093596059E-2</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L61" s="3">
         <f t="shared" si="7"/>
@@ -7105,13 +7105,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>1.379310344827586E-2</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
       </c>
       <c r="L62" s="3">
         <f t="shared" si="7"/>
@@ -7201,13 +7201,13 @@
         <v>0</v>
       </c>
       <c r="I63" s="3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K63" s="3">
         <v>9.852216748768473E-3</v>
-      </c>
-      <c r="J63" s="3">
-        <v>0</v>
-      </c>
-      <c r="K63" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L63" s="3">
         <f t="shared" si="7"/>
@@ -7297,13 +7297,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J64" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K64" s="3">
         <v>9.852216748768473E-3</v>
-      </c>
-      <c r="J64" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K64" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L64" s="3">
         <f t="shared" si="7"/>
@@ -7393,13 +7393,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3">
         <v>8.3743842364532011E-3</v>
-      </c>
-      <c r="J65" s="3">
-        <v>0</v>
-      </c>
-      <c r="K65" s="3">
-        <v>0</v>
       </c>
       <c r="L65" s="3">
         <f t="shared" si="7"/>
@@ -7489,13 +7489,13 @@
         <v>0</v>
       </c>
       <c r="I66" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3">
         <v>6.4039408866995084E-3</v>
-      </c>
-      <c r="J66" s="3">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
       </c>
       <c r="L66" s="3">
         <f t="shared" ref="L66:L97" si="13">1/96</f>
@@ -7585,13 +7585,13 @@
         <v>0</v>
       </c>
       <c r="I67" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J67" s="3">
+        <v>2.3809523809523812E-2</v>
+      </c>
+      <c r="K67" s="3">
         <v>7.3891625615763543E-3</v>
-      </c>
-      <c r="J67" s="3">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K67" s="3">
-        <v>2.3809523809523812E-2</v>
       </c>
       <c r="L67" s="3">
         <f t="shared" si="13"/>
@@ -7681,13 +7681,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I68" s="3">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K68" s="3">
         <v>6.8965517241379309E-3</v>
-      </c>
-      <c r="J68" s="3">
-        <v>0</v>
-      </c>
-      <c r="K68" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L68" s="3">
         <f t="shared" si="13"/>
@@ -7777,13 +7777,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <v>2.3809523809523812E-2</v>
+      </c>
+      <c r="K69" s="3">
         <v>6.4039408866995084E-3</v>
-      </c>
-      <c r="J69" s="3">
-        <v>0</v>
-      </c>
-      <c r="K69" s="3">
-        <v>2.3809523809523812E-2</v>
       </c>
       <c r="L69" s="3">
         <f t="shared" si="13"/>
@@ -7873,13 +7873,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K70" s="3">
         <v>4.9261083743842374E-3</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
-      <c r="K70" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L70" s="3">
         <f t="shared" si="13"/>
@@ -7969,13 +7969,13 @@
         <v>0</v>
       </c>
       <c r="I71" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J71" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K71" s="3">
         <v>8.3743842364532011E-3</v>
-      </c>
-      <c r="J71" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K71" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L71" s="3">
         <f t="shared" si="13"/>
@@ -8065,13 +8065,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I72" s="3">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="K72" s="3">
         <v>9.3596059113300496E-3</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
-      </c>
-      <c r="K72" s="3">
-        <v>3.5714285714285712E-2</v>
       </c>
       <c r="L72" s="3">
         <f t="shared" si="13"/>
@@ -8161,13 +8161,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I73" s="3">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K73" s="3">
         <v>6.4039408866995084E-3</v>
-      </c>
-      <c r="J73" s="3">
-        <v>0</v>
-      </c>
-      <c r="K73" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L73" s="3">
         <f t="shared" si="13"/>
@@ -8257,13 +8257,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K74" s="3">
         <v>9.852216748768473E-3</v>
-      </c>
-      <c r="J74" s="3">
-        <v>0</v>
-      </c>
-      <c r="K74" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L74" s="3">
         <f t="shared" si="13"/>
@@ -8353,13 +8353,13 @@
         <v>0</v>
       </c>
       <c r="I75" s="3">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3">
+        <v>4.7619047619047623E-2</v>
+      </c>
+      <c r="K75" s="3">
         <v>1.6748768472906399E-2</v>
-      </c>
-      <c r="J75" s="3">
-        <v>0</v>
-      </c>
-      <c r="K75" s="3">
-        <v>4.7619047619047623E-2</v>
       </c>
       <c r="L75" s="3">
         <f t="shared" si="13"/>
@@ -8449,13 +8449,13 @@
         <v>0</v>
       </c>
       <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="K76" s="3">
         <v>1.280788177339902E-2</v>
-      </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
-      <c r="K76" s="3">
-        <v>3.5714285714285712E-2</v>
       </c>
       <c r="L76" s="3">
         <f t="shared" si="13"/>
@@ -8545,13 +8545,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I77" s="3">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3">
+        <v>2.976190476190476E-2</v>
+      </c>
+      <c r="K77" s="3">
         <v>1.6748768472906399E-2</v>
-      </c>
-      <c r="J77" s="3">
-        <v>0</v>
-      </c>
-      <c r="K77" s="3">
-        <v>2.976190476190476E-2</v>
       </c>
       <c r="L77" s="3">
         <f t="shared" si="13"/>
@@ -8641,13 +8641,13 @@
         <v>0</v>
       </c>
       <c r="I78" s="3">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3">
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="K78" s="3">
         <v>2.2167487684729061E-2</v>
-      </c>
-      <c r="J78" s="3">
-        <v>0</v>
-      </c>
-      <c r="K78" s="3">
-        <v>7.1428571428571425E-2</v>
       </c>
       <c r="L78" s="3">
         <f t="shared" si="13"/>
@@ -8737,13 +8737,13 @@
         <v>0</v>
       </c>
       <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3">
+        <v>4.1666666666666657E-2</v>
+      </c>
+      <c r="K79" s="3">
         <v>2.9064039408866999E-2</v>
-      </c>
-      <c r="J79" s="3">
-        <v>0</v>
-      </c>
-      <c r="K79" s="3">
-        <v>4.1666666666666657E-2</v>
       </c>
       <c r="L79" s="3">
         <f t="shared" si="13"/>
@@ -8833,13 +8833,13 @@
         <v>0</v>
       </c>
       <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3">
+        <v>5.9523809523809521E-2</v>
+      </c>
+      <c r="K80" s="3">
         <v>3.0049261083743839E-2</v>
-      </c>
-      <c r="J80" s="3">
-        <v>0</v>
-      </c>
-      <c r="K80" s="3">
-        <v>5.9523809523809521E-2</v>
       </c>
       <c r="L80" s="3">
         <f t="shared" si="13"/>
@@ -8929,13 +8929,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
+        <v>4.7619047619047623E-2</v>
+      </c>
+      <c r="K81" s="3">
         <v>2.9064039408866999E-2</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
-        <v>4.7619047619047623E-2</v>
       </c>
       <c r="L81" s="3">
         <f t="shared" si="13"/>
@@ -9025,13 +9025,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I82" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J82" s="3">
+        <v>4.1666666666666657E-2</v>
+      </c>
+      <c r="K82" s="3">
         <v>2.9556650246305421E-2</v>
-      </c>
-      <c r="J82" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K82" s="3">
-        <v>4.1666666666666657E-2</v>
       </c>
       <c r="L82" s="3">
         <f t="shared" si="13"/>
@@ -9121,13 +9121,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I83" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J83" s="3">
+        <v>5.3571428571428568E-2</v>
+      </c>
+      <c r="K83" s="3">
         <v>3.5960591133004927E-2</v>
-      </c>
-      <c r="J83" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K83" s="3">
-        <v>5.3571428571428568E-2</v>
       </c>
       <c r="L83" s="3">
         <f t="shared" si="13"/>
@@ -9217,13 +9217,13 @@
         <v>0</v>
       </c>
       <c r="I84" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J84" s="3">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="K84" s="3">
         <v>3.5960591133004927E-2</v>
-      </c>
-      <c r="J84" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K84" s="3">
-        <v>3.5714285714285712E-2</v>
       </c>
       <c r="L84" s="3">
         <f t="shared" si="13"/>
@@ -9313,13 +9313,13 @@
         <v>0</v>
       </c>
       <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3">
+        <v>4.1666666666666657E-2</v>
+      </c>
+      <c r="K85" s="3">
         <v>3.0049261083743839E-2</v>
-      </c>
-      <c r="J85" s="3">
-        <v>0</v>
-      </c>
-      <c r="K85" s="3">
-        <v>4.1666666666666657E-2</v>
       </c>
       <c r="L85" s="3">
         <f t="shared" si="13"/>
@@ -9409,13 +9409,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="K86" s="3">
         <v>2.5123152709359609E-2</v>
-      </c>
-      <c r="J86" s="3">
-        <v>0</v>
-      </c>
-      <c r="K86" s="3">
-        <v>3.5714285714285712E-2</v>
       </c>
       <c r="L86" s="3">
         <f t="shared" si="13"/>
@@ -9505,13 +9505,13 @@
         <v>0</v>
       </c>
       <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3">
+        <v>2.976190476190476E-2</v>
+      </c>
+      <c r="K87" s="3">
         <v>2.5123152709359609E-2</v>
-      </c>
-      <c r="J87" s="3">
-        <v>0</v>
-      </c>
-      <c r="K87" s="3">
-        <v>2.976190476190476E-2</v>
       </c>
       <c r="L87" s="3">
         <f t="shared" si="13"/>
@@ -9601,13 +9601,13 @@
         <v>0</v>
       </c>
       <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3">
+        <v>4.1666666666666657E-2</v>
+      </c>
+      <c r="K88" s="3">
         <v>2.0197044334975371E-2</v>
-      </c>
-      <c r="J88" s="3">
-        <v>0</v>
-      </c>
-      <c r="K88" s="3">
-        <v>4.1666666666666657E-2</v>
       </c>
       <c r="L88" s="3">
         <f t="shared" si="13"/>
@@ -9697,13 +9697,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>1.231527093596059E-2</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
       </c>
       <c r="L89" s="3">
         <f t="shared" si="13"/>
@@ -9793,13 +9793,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K90" s="3">
         <v>5.9113300492610842E-3</v>
-      </c>
-      <c r="J90" s="3">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L90" s="3">
         <f t="shared" si="13"/>
@@ -9889,13 +9889,13 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K91" s="3">
         <v>9.3596059113300496E-3</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L91" s="3">
         <f t="shared" si="13"/>
@@ -9985,13 +9985,13 @@
         <v>0</v>
       </c>
       <c r="I92" s="3">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K92" s="3">
         <v>3.9408866995073889E-3</v>
-      </c>
-      <c r="J92" s="3">
-        <v>0</v>
-      </c>
-      <c r="K92" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L92" s="3">
         <f t="shared" si="13"/>
@@ -10081,13 +10081,13 @@
         <v>0</v>
       </c>
       <c r="I93" s="3">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3">
+        <v>0</v>
+      </c>
+      <c r="K93" s="3">
         <v>4.9261083743842374E-3</v>
-      </c>
-      <c r="J93" s="3">
-        <v>0</v>
-      </c>
-      <c r="K93" s="3">
-        <v>0</v>
       </c>
       <c r="L93" s="3">
         <f t="shared" si="13"/>
@@ -10177,13 +10177,13 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K94" s="3">
         <v>3.9408866995073889E-3</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L94" s="3">
         <f t="shared" si="13"/>
@@ -10273,13 +10273,13 @@
         <v>0</v>
       </c>
       <c r="I95" s="3">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3">
         <v>9.8522167487684722E-4</v>
-      </c>
-      <c r="J95" s="3">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3">
-        <v>0</v>
       </c>
       <c r="L95" s="3">
         <f t="shared" si="13"/>
@@ -10369,13 +10369,13 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>4.9261083743842361E-4</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
       </c>
       <c r="L96" s="3">
         <f t="shared" si="13"/>
@@ -10465,13 +10465,13 @@
         <v>0</v>
       </c>
       <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3">
         <v>1.477832512315271E-3</v>
-      </c>
-      <c r="J97" s="3">
-        <v>0</v>
-      </c>
-      <c r="K97" s="3">
-        <v>0</v>
       </c>
       <c r="L97" s="3">
         <f t="shared" si="13"/>
@@ -10550,7 +10550,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D97 G2:H97 J2:K97 Q2:S97 V2:Y97 AC2:AC97">
+  <conditionalFormatting sqref="C2:D97 G2:J97 Q2:S97 V2:Y97 AC2:AC97">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -10586,7 +10586,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I97">
+  <conditionalFormatting sqref="K2:K97">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -10729,31 +10729,31 @@
         <v>3</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>8</v>
@@ -10762,16 +10762,16 @@
         <v>9</v>
       </c>
       <c r="T1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="V1" s="7" t="s">
         <v>111</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X1" s="7" t="s">
         <v>10</v>
@@ -10780,13 +10780,13 @@
         <v>109</v>
       </c>
       <c r="Z1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="AC1" s="7" t="s">
         <v>11</v>
@@ -12718,13 +12718,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>1.169590643274854E-3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="2"/>
@@ -12813,13 +12813,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>2.3391812865497081E-3</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
       </c>
       <c r="L23" s="3">
         <f t="shared" si="2"/>
@@ -12908,13 +12908,13 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>3.508771929824561E-3</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="2"/>
@@ -13003,13 +13003,13 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
         <v>2.3391812865497081E-3</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" si="2"/>
@@ -13098,13 +13098,13 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>7.0175438596491229E-3</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="2"/>
@@ -13193,13 +13193,13 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>4.6783625730994153E-3</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="2"/>
@@ -13288,13 +13288,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
         <v>8.1871345029239772E-3</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="2"/>
@@ -13383,13 +13383,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>8.1871345029239772E-3</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="2"/>
@@ -13478,13 +13478,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
         <v>8.1871345029239772E-3</v>
-      </c>
-      <c r="J30" s="3">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3">
-        <v>0</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" si="2"/>
@@ -13573,13 +13573,13 @@
         <v>0</v>
       </c>
       <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
         <v>1.5204678362573099E-2</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3">
-        <v>0</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" si="2"/>
@@ -13668,13 +13668,13 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>1.6374269005847951E-2</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" si="2"/>
@@ -13763,13 +13763,13 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>2.5730994152046782E-2</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
       </c>
       <c r="L33" s="3">
         <f t="shared" si="2"/>
@@ -13858,13 +13858,13 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
         <v>1.988304093567252E-2</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0</v>
       </c>
       <c r="L34" s="3">
         <f t="shared" si="2"/>
@@ -13953,13 +13953,13 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>1.988304093567252E-2</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
       </c>
       <c r="L35" s="3">
         <f t="shared" si="2"/>
@@ -14048,13 +14048,13 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
         <v>1.1695906432748541E-2</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0</v>
       </c>
       <c r="L36" s="3">
         <f t="shared" si="2"/>
@@ -14143,13 +14143,13 @@
         <v>0.125</v>
       </c>
       <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K37" s="3">
         <v>1.1695906432748541E-2</v>
-      </c>
-      <c r="J37" s="3">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L37" s="3">
         <f t="shared" si="2"/>
@@ -14238,13 +14238,13 @@
         <v>0</v>
       </c>
       <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K38" s="3">
         <v>1.4035087719298249E-2</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0</v>
-      </c>
-      <c r="K38" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L38" s="3">
         <f t="shared" si="2"/>
@@ -14333,13 +14333,13 @@
         <v>0</v>
       </c>
       <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0</v>
+      </c>
+      <c r="K39" s="3">
         <v>1.1695906432748541E-2</v>
-      </c>
-      <c r="J39" s="3">
-        <v>0</v>
-      </c>
-      <c r="K39" s="3">
-        <v>0</v>
       </c>
       <c r="L39" s="3">
         <f t="shared" si="2"/>
@@ -14428,13 +14428,13 @@
         <v>0.125</v>
       </c>
       <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K40" s="3">
         <v>1.1695906432748541E-2</v>
-      </c>
-      <c r="J40" s="3">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L40" s="3">
         <f t="shared" si="2"/>
@@ -14523,13 +14523,13 @@
         <v>0</v>
       </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>1.1695906432748541E-2</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
       </c>
       <c r="L41" s="3">
         <f t="shared" si="2"/>
@@ -14618,13 +14618,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>7.0175438596491229E-3</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
       </c>
       <c r="L42" s="3">
         <f t="shared" si="2"/>
@@ -14713,13 +14713,13 @@
         <v>0.125</v>
       </c>
       <c r="I43" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K43" s="3">
         <v>7.0175438596491229E-3</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L43" s="3">
         <f t="shared" si="2"/>
@@ -14808,13 +14808,13 @@
         <v>0</v>
       </c>
       <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
         <v>9.3567251461988306E-3</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
       </c>
       <c r="L44" s="3">
         <f t="shared" si="2"/>
@@ -14903,13 +14903,13 @@
         <v>0</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>1.4035087719298249E-2</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
       </c>
       <c r="L45" s="3">
         <f t="shared" si="2"/>
@@ -14998,13 +14998,13 @@
         <v>0</v>
       </c>
       <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K46" s="3">
         <v>1.4035087719298249E-2</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0</v>
-      </c>
-      <c r="K46" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L46" s="3">
         <f t="shared" si="2"/>
@@ -15093,13 +15093,13 @@
         <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>7.0175438596491229E-3</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
       </c>
       <c r="L47" s="3">
         <f t="shared" si="2"/>
@@ -15188,13 +15188,13 @@
         <v>0</v>
       </c>
       <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K48" s="3">
         <v>5.8479532163742687E-3</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L48" s="3">
         <f t="shared" si="2"/>
@@ -15283,13 +15283,13 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J49" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K49" s="3">
         <v>1.0526315789473681E-2</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K49" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L49" s="3">
         <f t="shared" si="2"/>
@@ -15378,13 +15378,13 @@
         <v>0</v>
       </c>
       <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K50" s="3">
         <v>1.754385964912281E-2</v>
-      </c>
-      <c r="J50" s="3">
-        <v>0</v>
-      </c>
-      <c r="K50" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L50" s="3">
         <f t="shared" si="2"/>
@@ -15473,13 +15473,13 @@
         <v>0.125</v>
       </c>
       <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K51" s="3">
         <v>1.6374269005847951E-2</v>
-      </c>
-      <c r="J51" s="3">
-        <v>0</v>
-      </c>
-      <c r="K51" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L51" s="3">
         <f t="shared" si="2"/>
@@ -15568,13 +15568,13 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K52" s="3">
         <v>1.8713450292397661E-2</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L52" s="3">
         <f t="shared" si="2"/>
@@ -15663,13 +15663,13 @@
         <v>0</v>
       </c>
       <c r="I53" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J53" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K53" s="3">
         <v>1.6374269005847951E-2</v>
-      </c>
-      <c r="J53" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="K53" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L53" s="3">
         <f t="shared" si="2"/>
@@ -15758,13 +15758,13 @@
         <v>0</v>
       </c>
       <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K54" s="3">
         <v>1.6374269005847951E-2</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L54" s="3">
         <f t="shared" si="2"/>
@@ -15853,13 +15853,13 @@
         <v>0</v>
       </c>
       <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K55" s="3">
         <v>2.923976608187134E-2</v>
-      </c>
-      <c r="J55" s="3">
-        <v>0</v>
-      </c>
-      <c r="K55" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L55" s="3">
         <f t="shared" si="2"/>
@@ -15948,13 +15948,13 @@
         <v>0.125</v>
       </c>
       <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K56" s="3">
         <v>1.1695906432748541E-2</v>
-      </c>
-      <c r="J56" s="3">
-        <v>0</v>
-      </c>
-      <c r="K56" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L56" s="3">
         <f t="shared" si="2"/>
@@ -16043,13 +16043,13 @@
         <v>0</v>
       </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K57" s="3">
         <v>2.5730994152046782E-2</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L57" s="3">
         <f t="shared" si="2"/>
@@ -16138,13 +16138,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K58" s="3">
         <v>2.222222222222222E-2</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L58" s="3">
         <f t="shared" si="2"/>
@@ -16233,13 +16233,13 @@
         <v>0</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>1.6374269005847951E-2</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
       </c>
       <c r="L59" s="3">
         <f t="shared" si="2"/>
@@ -16328,13 +16328,13 @@
         <v>0</v>
       </c>
       <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K60" s="3">
         <v>4.6783625730994153E-3</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L60" s="3">
         <f t="shared" si="2"/>
@@ -16423,13 +16423,13 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>5.7971014492753617E-2</v>
+      </c>
+      <c r="K61" s="3">
         <v>1.754385964912281E-2</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>5.7971014492753617E-2</v>
       </c>
       <c r="L61" s="3">
         <f t="shared" si="2"/>
@@ -16518,13 +16518,13 @@
         <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K62" s="3">
         <v>8.1871345029239772E-3</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L62" s="3">
         <f t="shared" si="2"/>
@@ -16613,13 +16613,13 @@
         <v>0</v>
       </c>
       <c r="I63" s="3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K63" s="3">
         <v>9.3567251461988306E-3</v>
-      </c>
-      <c r="J63" s="3">
-        <v>0</v>
-      </c>
-      <c r="K63" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L63" s="3">
         <f t="shared" si="2"/>
@@ -16708,13 +16708,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="3">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>4.3478260869565223E-2</v>
+      </c>
+      <c r="K64" s="3">
         <v>1.0526315789473681E-2</v>
-      </c>
-      <c r="J64" s="3">
-        <v>0</v>
-      </c>
-      <c r="K64" s="3">
-        <v>4.3478260869565223E-2</v>
       </c>
       <c r="L64" s="3">
         <f t="shared" si="2"/>
@@ -16803,13 +16803,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K65" s="3">
         <v>1.2865497076023391E-2</v>
-      </c>
-      <c r="J65" s="3">
-        <v>0</v>
-      </c>
-      <c r="K65" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L65" s="3">
         <f t="shared" si="2"/>
@@ -16898,13 +16898,13 @@
         <v>0</v>
       </c>
       <c r="I66" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3">
         <v>5.8479532163742687E-3</v>
-      </c>
-      <c r="J66" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
       </c>
       <c r="L66" s="3">
         <f t="shared" si="2"/>
@@ -16993,13 +16993,13 @@
         <v>0.125</v>
       </c>
       <c r="I67" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J67" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K67" s="3">
         <v>9.3567251461988306E-3</v>
-      </c>
-      <c r="J67" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K67" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L67" s="3">
         <f t="shared" ref="L67:L97" si="7">1/96</f>
@@ -17088,13 +17088,13 @@
         <v>0</v>
       </c>
       <c r="I68" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J68" s="3">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3">
         <v>4.6783625730994153E-3</v>
-      </c>
-      <c r="J68" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K68" s="3">
-        <v>0</v>
       </c>
       <c r="L68" s="3">
         <f t="shared" si="7"/>
@@ -17183,13 +17183,13 @@
         <v>0</v>
       </c>
       <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <v>0</v>
+      </c>
+      <c r="K69" s="3">
         <v>8.1871345029239772E-3</v>
-      </c>
-      <c r="J69" s="3">
-        <v>0</v>
-      </c>
-      <c r="K69" s="3">
-        <v>0</v>
       </c>
       <c r="L69" s="3">
         <f t="shared" si="7"/>
@@ -17278,13 +17278,13 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K70" s="3">
         <v>7.0175438596491229E-3</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
-      <c r="K70" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L70" s="3">
         <f t="shared" si="7"/>
@@ -17373,13 +17373,13 @@
         <v>0</v>
       </c>
       <c r="I71" s="3">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K71" s="3">
         <v>8.1871345029239772E-3</v>
-      </c>
-      <c r="J71" s="3">
-        <v>0</v>
-      </c>
-      <c r="K71" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L71" s="3">
         <f t="shared" si="7"/>
@@ -17468,13 +17468,13 @@
         <v>0</v>
       </c>
       <c r="I72" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J72" s="3">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3">
         <v>8.1871345029239772E-3</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K72" s="3">
-        <v>0</v>
       </c>
       <c r="L72" s="3">
         <f t="shared" si="7"/>
@@ -17563,13 +17563,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="3">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3">
         <v>8.1871345029239772E-3</v>
-      </c>
-      <c r="J73" s="3">
-        <v>0</v>
-      </c>
-      <c r="K73" s="3">
-        <v>0</v>
       </c>
       <c r="L73" s="3">
         <f t="shared" si="7"/>
@@ -17658,13 +17658,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3">
+        <v>0</v>
+      </c>
+      <c r="K74" s="3">
         <v>7.0175438596491229E-3</v>
-      </c>
-      <c r="J74" s="3">
-        <v>0</v>
-      </c>
-      <c r="K74" s="3">
-        <v>0</v>
       </c>
       <c r="L74" s="3">
         <f t="shared" si="7"/>
@@ -17753,13 +17753,13 @@
         <v>0</v>
       </c>
       <c r="I75" s="3">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K75" s="3">
         <v>9.3567251461988306E-3</v>
-      </c>
-      <c r="J75" s="3">
-        <v>0</v>
-      </c>
-      <c r="K75" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L75" s="3">
         <f t="shared" si="7"/>
@@ -17848,13 +17848,13 @@
         <v>0.125</v>
       </c>
       <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K76" s="3">
         <v>1.8713450292397661E-2</v>
-      </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
-      <c r="K76" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L76" s="3">
         <f t="shared" si="7"/>
@@ -17943,13 +17943,13 @@
         <v>0</v>
       </c>
       <c r="I77" s="3">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K77" s="3">
         <v>1.5204678362573099E-2</v>
-      </c>
-      <c r="J77" s="3">
-        <v>0</v>
-      </c>
-      <c r="K77" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L77" s="3">
         <f t="shared" si="7"/>
@@ -18038,13 +18038,13 @@
         <v>0</v>
       </c>
       <c r="I78" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J78" s="3">
+        <v>0</v>
+      </c>
+      <c r="K78" s="3">
         <v>2.3391812865497071E-2</v>
-      </c>
-      <c r="J78" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K78" s="3">
-        <v>0</v>
       </c>
       <c r="L78" s="3">
         <f t="shared" si="7"/>
@@ -18133,13 +18133,13 @@
         <v>0</v>
       </c>
       <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K79" s="3">
         <v>2.690058479532164E-2</v>
-      </c>
-      <c r="J79" s="3">
-        <v>0</v>
-      </c>
-      <c r="K79" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L79" s="3">
         <f t="shared" si="7"/>
@@ -18228,13 +18228,13 @@
         <v>0</v>
       </c>
       <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3">
+        <v>4.3478260869565223E-2</v>
+      </c>
+      <c r="K80" s="3">
         <v>2.456140350877193E-2</v>
-      </c>
-      <c r="J80" s="3">
-        <v>0</v>
-      </c>
-      <c r="K80" s="3">
-        <v>4.3478260869565223E-2</v>
       </c>
       <c r="L80" s="3">
         <f t="shared" si="7"/>
@@ -18323,13 +18323,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K81" s="3">
         <v>2.3391812865497071E-2</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L81" s="3">
         <f t="shared" si="7"/>
@@ -18418,13 +18418,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K82" s="3">
         <v>3.9766081871345033E-2</v>
-      </c>
-      <c r="J82" s="3">
-        <v>0</v>
-      </c>
-      <c r="K82" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L82" s="3">
         <f t="shared" si="7"/>
@@ -18513,13 +18513,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K83" s="3">
         <v>2.923976608187134E-2</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L83" s="3">
         <f t="shared" si="7"/>
@@ -18608,13 +18608,13 @@
         <v>0</v>
       </c>
       <c r="I84" s="3">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3">
+        <v>5.7971014492753617E-2</v>
+      </c>
+      <c r="K84" s="3">
         <v>2.8070175438596488E-2</v>
-      </c>
-      <c r="J84" s="3">
-        <v>0</v>
-      </c>
-      <c r="K84" s="3">
-        <v>5.7971014492753617E-2</v>
       </c>
       <c r="L84" s="3">
         <f t="shared" si="7"/>
@@ -18703,13 +18703,13 @@
         <v>0.125</v>
       </c>
       <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3">
+        <v>4.3478260869565223E-2</v>
+      </c>
+      <c r="K85" s="3">
         <v>2.456140350877193E-2</v>
-      </c>
-      <c r="J85" s="3">
-        <v>0</v>
-      </c>
-      <c r="K85" s="3">
-        <v>4.3478260869565223E-2</v>
       </c>
       <c r="L85" s="3">
         <f t="shared" si="7"/>
@@ -18798,13 +18798,13 @@
         <v>0</v>
       </c>
       <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K86" s="3">
         <v>3.7426900584795322E-2</v>
-      </c>
-      <c r="J86" s="3">
-        <v>0</v>
-      </c>
-      <c r="K86" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L86" s="3">
         <f t="shared" si="7"/>
@@ -18893,13 +18893,13 @@
         <v>0</v>
       </c>
       <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K87" s="3">
         <v>2.1052631578947371E-2</v>
-      </c>
-      <c r="J87" s="3">
-        <v>0</v>
-      </c>
-      <c r="K87" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L87" s="3">
         <f t="shared" si="7"/>
@@ -18988,13 +18988,13 @@
         <v>0</v>
       </c>
       <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K88" s="3">
         <v>1.988304093567252E-2</v>
-      </c>
-      <c r="J88" s="3">
-        <v>0</v>
-      </c>
-      <c r="K88" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L88" s="3">
         <f t="shared" si="7"/>
@@ -19083,13 +19083,13 @@
         <v>0</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K89" s="3">
         <v>1.2865497076023391E-2</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L89" s="3">
         <f t="shared" si="7"/>
@@ -19178,13 +19178,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K90" s="3">
         <v>8.1871345029239772E-3</v>
-      </c>
-      <c r="J90" s="3">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L90" s="3">
         <f t="shared" si="7"/>
@@ -19273,13 +19273,13 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>7.0175438596491229E-3</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
       </c>
       <c r="L91" s="3">
         <f t="shared" si="7"/>
@@ -19368,13 +19368,13 @@
         <v>0</v>
       </c>
       <c r="I92" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J92" s="3">
+        <v>0</v>
+      </c>
+      <c r="K92" s="3">
         <v>1.0526315789473681E-2</v>
-      </c>
-      <c r="J92" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K92" s="3">
-        <v>0</v>
       </c>
       <c r="L92" s="3">
         <f t="shared" si="7"/>
@@ -19463,13 +19463,13 @@
         <v>0</v>
       </c>
       <c r="I93" s="3">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K93" s="3">
         <v>2.3391812865497081E-3</v>
-      </c>
-      <c r="J93" s="3">
-        <v>0</v>
-      </c>
-      <c r="K93" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L93" s="3">
         <f t="shared" si="7"/>
@@ -19558,13 +19558,13 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>3.508771929824561E-3</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
       </c>
       <c r="L94" s="3">
         <f t="shared" si="7"/>
@@ -19653,13 +19653,13 @@
         <v>0</v>
       </c>
       <c r="I95" s="3">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K95" s="3">
         <v>1.169590643274854E-3</v>
-      </c>
-      <c r="J95" s="3">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L95" s="3">
         <f t="shared" si="7"/>
@@ -19748,13 +19748,13 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K96" s="3">
         <v>1.169590643274854E-3</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L96" s="3">
         <f t="shared" si="7"/>
@@ -19843,13 +19843,13 @@
         <v>0</v>
       </c>
       <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3">
         <v>1.169590643274854E-3</v>
-      </c>
-      <c r="J97" s="3">
-        <v>0</v>
-      </c>
-      <c r="K97" s="3">
-        <v>0</v>
       </c>
       <c r="L97" s="3">
         <f t="shared" si="7"/>
@@ -19931,7 +19931,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D97 F2:H97 J2:L97 Q2:V97 Y2:AC97">
+  <conditionalFormatting sqref="C2:D97 F2:J97 L2:L97 Q2:V97 Y2:AC97">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -19955,7 +19955,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I97">
+  <conditionalFormatting sqref="K2:K97">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>

--- a/files/energy/input/load_emulator/input_emulator_v2/1. usage_probability_v2.xlsx
+++ b/files/energy/input/load_emulator/input_emulator_v2/1. usage_probability_v2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="339" documentId="11_59AB53411A6BFA624CF54379889ED3FCF7CC7820" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0789455C-878B-4E2D-B68D-27B270BE89A1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="working_day" sheetId="1" r:id="rId1"/>

--- a/files/energy/input/load_emulator/input_emulator_v2/1. usage_probability_v2.xlsx
+++ b/files/energy/input/load_emulator/input_emulator_v2/1. usage_probability_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rsericerca-my.sharepoint.com/personal/rollo_rse-web_it/Documents/Desktop/CACER simulator - public repo/CACER-simulator/files/energy/input/load_emulator/input_emulator_v2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="339" documentId="11_59AB53411A6BFA624CF54379889ED3FCF7CC7820" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0789455C-878B-4E2D-B68D-27B270BE89A1}"/>
+  <xr:revisionPtr revIDLastSave="345" documentId="11_59AB53411A6BFA624CF54379889ED3FCF7CC7820" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D79F7F4-EC8B-46E3-B14F-D82F7B00482B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="working_day" sheetId="1" r:id="rId1"/>
@@ -19931,7 +19931,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D97 F2:J97 L2:L97 Q2:V97 Y2:AC97">
+  <conditionalFormatting sqref="C2:D97 F2:J97 L2:L97 Q2:V97 Y3:AC97 Z2:AC2">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -20015,7 +20015,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X97">
+  <conditionalFormatting sqref="X2:X97 Y2">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
